--- a/stockPicker/selected_cn_history.xlsx
+++ b/stockPicker/selected_cn_history.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,726 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>2026-01-03 00:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-06 11:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-06 11:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-07 11:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:43:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:43:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:43:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:43:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-01-07 18:43:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-08 18:56:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-01-08 19:46:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-01-08 19:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-01-08 19:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-01-08 19:47:00</t>
         </is>
       </c>
     </row>
@@ -731,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,20 +1504,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>600967</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.156</v>
+        <v>0.135</v>
       </c>
       <c r="D2" t="n">
-        <v>0.124</v>
+        <v>0.146</v>
       </c>
       <c r="E2" t="n">
-        <v>1.21</v>
+        <v>3.28</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -807,37 +1527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>002151</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-08 19:47:00</t>
         </is>
       </c>
     </row>
@@ -905,17 +1595,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>600118</t>
+          <t>600879</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.436</v>
+        <v>0.346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.496</v>
+        <v>0.339</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3</v>
+        <v>0.95</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -928,27 +1618,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-08 19:47:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300136</t>
+          <t>002195</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.386</v>
+        <v>0.494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.591</v>
+        <v>0.511</v>
       </c>
       <c r="E3" t="n">
-        <v>1.98</v>
+        <v>4.14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -958,7 +1648,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-08 19:47:00</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>600498, 002151</t>
+          <t>600967</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1755,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600118, 300136</t>
+          <t>600879, 002195</t>
         </is>
       </c>
     </row>

--- a/stockPicker/selected_cn_history.xlsx
+++ b/stockPicker/selected_cn_history.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,6 +1437,276 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>2026-01-08 19:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>300058</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>002131</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,30 +1774,120 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>600967</t>
+          <t>000547</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.135</v>
+        <v>0.145</v>
       </c>
       <c r="D2" t="n">
-        <v>0.146</v>
+        <v>0.219</v>
       </c>
       <c r="E2" t="n">
-        <v>3.28</v>
+        <v>1.04</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.65</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-01-08 19:47:00</t>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:38</t>
         </is>
       </c>
     </row>
@@ -1602,53 +1962,53 @@
         <v>0.346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.339</v>
+        <v>0.488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-08 19:47:00</t>
+          <t>2026-01-11 16:15:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>002195</t>
+          <t>002792</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.494</v>
+        <v>0.423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.511</v>
+        <v>0.431</v>
       </c>
       <c r="E3" t="n">
-        <v>4.14</v>
+        <v>0.87</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-08 19:47:00</t>
+          <t>2026-01-11 16:15:38</t>
         </is>
       </c>
     </row>
@@ -1745,7 +2105,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>600967</t>
+          <t>000547, 002340, 300604, 600111</t>
         </is>
       </c>
     </row>
@@ -1755,7 +2115,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600879, 002195</t>
+          <t>600879, 002792</t>
         </is>
       </c>
     </row>

--- a/stockPicker/selected_cn_history.xlsx
+++ b/stockPicker/selected_cn_history.xlsx
@@ -7,11 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History_7cacheData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_1_7cacheData" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_2_7cacheData" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_3_7cacheData" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_7cacheData" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History_onetime" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_1_onetime" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_2_onetime" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level_3_onetime" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_onetime" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,260 +488,260 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>000547</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.156</v>
+        <v>0.145</v>
       </c>
       <c r="D2" t="n">
-        <v>0.124</v>
+        <v>0.219</v>
       </c>
       <c r="E2" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-03 00:27:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>002151</t>
+          <t>002340</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.216</v>
+        <v>0.049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.247</v>
+        <v>0.096</v>
       </c>
       <c r="E3" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-03 00:27:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600118</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.436</v>
+        <v>0.22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.496</v>
+        <v>0.166</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-03 00:27:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300136</t>
+          <t>600111</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.386</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.591</v>
+        <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.98</v>
+        <v>2.61</v>
       </c>
       <c r="F5" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-01-03 00:27:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>600879</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.156</v>
+        <v>0.346</v>
       </c>
       <c r="D6" t="n">
-        <v>0.124</v>
+        <v>0.488</v>
       </c>
       <c r="E6" t="n">
-        <v>1.21</v>
+        <v>0.97</v>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002151</t>
+          <t>002792</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.216</v>
+        <v>0.423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.247</v>
+        <v>0.431</v>
       </c>
       <c r="E7" t="n">
-        <v>2.77</v>
+        <v>0.87</v>
       </c>
       <c r="F7" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600118</t>
+          <t>000547</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.436</v>
+        <v>0.145</v>
       </c>
       <c r="D8" t="n">
-        <v>0.496</v>
+        <v>0.219</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>300136</t>
+          <t>002340</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.386</v>
+        <v>0.049</v>
       </c>
       <c r="D9" t="n">
-        <v>0.591</v>
+        <v>0.096</v>
       </c>
       <c r="E9" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="F9" t="n">
-        <v>0.96</v>
+        <v>0.65</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-01-03 00:28:56</t>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>300059</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.064</v>
+        <v>0.22</v>
       </c>
       <c r="D10" t="n">
-        <v>0.082</v>
+        <v>0.166</v>
       </c>
       <c r="E10" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="F10" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -746,87 +751,87 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-01-06 11:14:17</t>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>600879</t>
+          <t>600111</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.229</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.414</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>1.08</v>
+        <v>2.61</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-01-06 11:14:17</t>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>300059</t>
+          <t>600879</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.051</v>
+        <v>0.346</v>
       </c>
       <c r="D12" t="n">
-        <v>0.051</v>
+        <v>0.488</v>
       </c>
       <c r="E12" t="n">
-        <v>1.88</v>
+        <v>0.97</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-01-07 11:21:27</t>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>600879</t>
+          <t>002792</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.23</v>
+        <v>0.423</v>
       </c>
       <c r="D13" t="n">
-        <v>0.274</v>
+        <v>0.431</v>
       </c>
       <c r="E13" t="n">
-        <v>1.05</v>
+        <v>0.87</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -836,878 +841,59 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-01-07 11:21:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>002340</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-01-07 11:25:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>300604</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-01-07 11:25:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>600111</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-01-07 11:25:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-01-07 11:25:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>002792</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-01-07 11:25:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>002340</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>300604</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>600111</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>002792</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>002340</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:43:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>300604</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:43:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>600111</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:43:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:43:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>002792</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-01-07 18:43:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>600879</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+          <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>002050, 600410, 002400</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>002131, 301171, 300063, 300058</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-01-08 18:56:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>600879</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-01-08 19:46:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>600967</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-01-08 19:47:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>600879</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-01-08 19:47:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>002195</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-01-08 19:47:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>600879</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-01-10 17:13:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>300058</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-01-10 17:13:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>002131</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-01-10 17:13:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>002340</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>300604</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>600111</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>600879</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>002792</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-01-11 16:15:38</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -1721,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,7 +983,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1013,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1043,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1073,127 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1978,7 +1284,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +1314,67 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-11 16:15:38</t>
+          <t>2026-01-11 16:31:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:09</t>
         </is>
       </c>
     </row>
@@ -2084,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +1490,695 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000547, 002340, 300604, 600111</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>600879, 002792</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ROE_Pct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>5D_Return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>7D_Return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price/High</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Appearances_7D</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>run_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>002050</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>600410</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>002400</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>002131</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>301171</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>300063</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>300058</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ROE_Pct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>5D_Return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>7D_Return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price/High</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Appearances_7D</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>run_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>002050</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>600410</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>002400</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ROE_Pct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>5D_Return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>7D_Return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price/High</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Appearances_7D</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>run_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>002131</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>301171</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>300063</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>300058</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ROE_Pct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>5D_Return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>7D_Return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price/High</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Appearances_7D</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>run_time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stockPicker/selected_cn_history.xlsx
+++ b/stockPicker/selected_cn_history.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +842,1686 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>002371</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.106</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.149</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
         </is>
       </c>
     </row>
@@ -856,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,6 +2573,96 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300059, 002600, 600839, 600111, 000066</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>600118, 000981, 002195, 002465</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>300059, 601216, 000725</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000981, 002195, 600879, 603000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>600584, 601669, 600111, 002156</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>600584, 002156, 601669</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -907,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,6 +2964,1116 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>002371</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>002340</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.106</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.149</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
         </is>
       </c>
     </row>
@@ -1208,7 +4088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,6 +4255,576 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>000547</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>002639</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:38:24</t>
         </is>
       </c>
     </row>
@@ -1450,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,6 +4962,151 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>600111, 300059, 002371, 002340, 300604</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>600879, 600118, 000981, 000547, 002792, 002195</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>300059, 600111, 002565, 000725, 002340, 300604</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>600879, 000981, 002195, 002792, 002639, 601179</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>600879, 300059, 600111, 002565, 000725, 002792, 300604</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>000981, 002195, 002639, 601179</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>600879, 000981, 600111, 002565, 000725, 002792, 002639, 300604</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002195, 601179</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>000981, 600879, 600111, 002195, 002792, 300604, 601179</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>000981, 600111, 002195, 300604</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1526,7 +5121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,6 +5378,696 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>002600</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>600839</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>000066</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>002465</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>603000</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
         </is>
       </c>
     </row>
@@ -1797,7 +6082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1934,6 +6219,456 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>002600</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>600839</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>000066</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:35:16</t>
         </is>
       </c>
     </row>
@@ -1948,7 +6683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,6 +6850,246 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>2026-01-11 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>002465</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>603000</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:16:12</t>
         </is>
       </c>
     </row>
